--- a/data/trans_orig/Q03B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q03B_R-Habitat-trans_orig.xlsx
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,62</t>
+          <t>1,38; 1,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,81</t>
+          <t>1,56; 1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,51</t>
+          <t>3,14; 3,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,05</t>
+          <t>3,69; 4,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 3,84</t>
+          <t>3,56; 3,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,17</t>
+          <t>1,95; 2,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 2,8</t>
+          <t>2,56; 2,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 2,83</t>
+          <t>2,59; 2,82</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,21</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,32 +797,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 1,85</t>
+          <t>1,64; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,77</t>
+          <t>3,47; 3,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 3,86</t>
+          <t>3,57; 3,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,7</t>
+          <t>3,45; 3,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,48</t>
+          <t>2,26; 2,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 2,68</t>
+          <t>2,46; 2,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,5</t>
+          <t>1,28; 1,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,27 +912,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 4,22</t>
+          <t>3,83; 4,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,59</t>
+          <t>3,28; 3,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,57</t>
+          <t>3,29; 3,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,0</t>
+          <t>2,73; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,53</t>
+          <t>2,32; 2,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,65</t>
+          <t>1,39; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,62</t>
+          <t>1,44; 1,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,46</t>
+          <t>3,17; 3,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,56</t>
+          <t>2,37; 2,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 2,48</t>
+          <t>2,31; 2,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 2,65</t>
+          <t>2,49; 2,66</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,33</t>
+          <t>1,2; 1,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 3,64</t>
+          <t>3,47; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 3,54</t>
+          <t>3,39; 3,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 2,67</t>
+          <t>2,57; 2,66</t>
         </is>
       </c>
     </row>
